--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302823C2-4445-E944-ACE1-5033A8FE0B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC1F6F-3F7D-7E42-BBF1-E14C05F01293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5800" yWindow="500" windowWidth="32600" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4240" yWindow="2460" windowWidth="32600" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
@@ -125,9 +125,6 @@
     <t>Accounting Period</t>
   </si>
   <si>
-    <t>GBP Amount</t>
-  </si>
-  <si>
     <t>Project Currency</t>
   </si>
   <si>
@@ -206,12 +203,6 @@
     <t>Feb-23</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Project ID</t>
-  </si>
-  <si>
     <t>11111995_11111999</t>
   </si>
   <si>
@@ -237,6 +228,15 @@
   </si>
   <si>
     <t>Vivaldi</t>
+  </si>
+  <si>
+    <t>Project Number</t>
+  </si>
+  <si>
+    <t>Amount (GBP)</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
 </sst>
 </file>
@@ -1045,9 +1045,11 @@
     <col min="5" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="12.1640625" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="10" width="1.1640625" customWidth="1"/>
-    <col min="11" max="12" width="1" customWidth="1"/>
-    <col min="13" max="13" width="1.33203125" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" customWidth="1"/>
+    <col min="11" max="11" width="5.5" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" customWidth="1"/>
     <col min="14" max="14" width="12.1640625" style="15" customWidth="1"/>
     <col min="15" max="16" width="9.1640625" customWidth="1"/>
     <col min="17" max="17" width="9.83203125" customWidth="1"/>
@@ -1103,9 +1105,9 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="240" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>17</v>
@@ -1147,22 +1149,22 @@
         <v>29</v>
       </c>
       <c r="O3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="T3" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1170,25 +1172,25 @@
         <v>14</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -1196,13 +1198,13 @@
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O4" s="7">
         <v>5208</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>
@@ -1212,7 +1214,7 @@
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1220,25 +1222,25 @@
         <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -1246,13 +1248,13 @@
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
       <c r="N5" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" s="7">
         <v>5208</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
@@ -1262,7 +1264,7 @@
       </c>
       <c r="S5" s="6"/>
       <c r="T5" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1270,25 +1272,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -1296,13 +1298,13 @@
       <c r="L6" s="6"/>
       <c r="M6" s="5"/>
       <c r="N6" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="7">
         <v>5208</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="7">
         <v>0</v>
@@ -1312,7 +1314,7 @@
       </c>
       <c r="S6" s="6"/>
       <c r="T6" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1320,25 +1322,25 @@
         <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -1346,13 +1348,13 @@
       <c r="L7" s="6"/>
       <c r="M7" s="5"/>
       <c r="N7" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7" s="7">
         <v>5208</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="7">
         <v>0</v>
@@ -1362,7 +1364,7 @@
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1370,25 +1372,25 @@
         <v>14</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -1396,13 +1398,13 @@
       <c r="L8" s="6"/>
       <c r="M8" s="5"/>
       <c r="N8" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O8" s="7">
         <v>5208</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
@@ -1412,7 +1414,7 @@
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1420,25 +1422,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -1446,13 +1448,13 @@
       <c r="L9" s="6"/>
       <c r="M9" s="5"/>
       <c r="N9" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O9" s="7">
         <v>500</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
@@ -1460,7 +1462,7 @@
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="64" x14ac:dyDescent="0.2">
@@ -1468,25 +1470,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -1494,13 +1496,13 @@
       <c r="L10" s="6"/>
       <c r="M10" s="5"/>
       <c r="N10" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O10" s="7">
         <v>600</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="7">
         <v>0</v>
@@ -1516,25 +1518,25 @@
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -1542,13 +1544,13 @@
       <c r="L11" s="6"/>
       <c r="M11" s="5"/>
       <c r="N11" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O11" s="7">
         <v>500</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="7">
         <v>0</v>
@@ -1561,28 +1563,28 @@
     </row>
     <row r="12" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -1590,13 +1592,13 @@
       <c r="L12" s="6"/>
       <c r="M12" s="5"/>
       <c r="N12" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O12" s="7">
         <v>3300</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="7">
         <v>0</v>
@@ -1606,33 +1608,33 @@
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -1640,13 +1642,13 @@
       <c r="L13" s="6"/>
       <c r="M13" s="5"/>
       <c r="N13" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" s="7">
         <v>3300</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="7">
         <v>0</v>
@@ -1656,33 +1658,33 @@
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -1690,13 +1692,13 @@
       <c r="L14" s="6"/>
       <c r="M14" s="5"/>
       <c r="N14" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O14" s="7">
         <v>3000</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="7">
         <v>0</v>
@@ -1706,33 +1708,33 @@
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -1740,13 +1742,13 @@
       <c r="L15" s="6"/>
       <c r="M15" s="5"/>
       <c r="N15" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O15" s="7">
         <v>2000</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q15" s="7">
         <v>0</v>
@@ -1756,33 +1758,33 @@
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -1790,13 +1792,13 @@
       <c r="L16" s="6"/>
       <c r="M16" s="5"/>
       <c r="N16" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O16" s="7">
         <v>6000</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="7">
         <v>0</v>
@@ -1806,33 +1808,33 @@
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -1840,13 +1842,13 @@
       <c r="L17" s="6"/>
       <c r="M17" s="5"/>
       <c r="N17" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O17" s="7">
         <v>6000</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="7">
         <v>0</v>
@@ -1856,33 +1858,33 @@
       </c>
       <c r="S17" s="6"/>
       <c r="T17" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -1890,13 +1892,13 @@
       <c r="L18" s="6"/>
       <c r="M18" s="5"/>
       <c r="N18" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O18" s="7">
         <v>6000</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q18" s="7">
         <v>0</v>
@@ -1906,33 +1908,33 @@
       </c>
       <c r="S18" s="6"/>
       <c r="T18" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -1940,13 +1942,13 @@
       <c r="L19" s="6"/>
       <c r="M19" s="5"/>
       <c r="N19" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" s="7">
         <v>6000</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q19" s="7">
         <v>0</v>
@@ -1956,7 +1958,7 @@
       </c>
       <c r="S19" s="6"/>
       <c r="T19" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2016,7 +2018,7 @@
     </row>
     <row r="2" spans="1:20" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2065,16 +2067,16 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>20</v>
@@ -2086,13 +2088,13 @@
         <v>27</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="1"/>

--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC1F6F-3F7D-7E42-BBF1-E14C05F01293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3776B028-3EBA-F449-A8A7-092790244520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2460" windowWidth="32600" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="600" windowWidth="33460" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="71">
   <si>
     <t>PROJECT SUMMARY</t>
   </si>
@@ -206,15 +206,6 @@
     <t>11111995_11111999</t>
   </si>
   <si>
-    <t xml:space="preserve">10_2019_Stfc 114257 Dr F. Bloggs  </t>
-  </si>
-  <si>
-    <t>10_2019_Stfc 114257 Dr F. Bloggs</t>
-  </si>
-  <si>
-    <t>10_2019_Stfc 114999 Jones</t>
-  </si>
-  <si>
     <t>Consumables - Telephone and Communication</t>
   </si>
   <si>
@@ -227,9 +218,6 @@
     <t>Aug-22</t>
   </si>
   <si>
-    <t>Vivaldi</t>
-  </si>
-  <si>
     <t>Project Number</t>
   </si>
   <si>
@@ -237,13 +225,34 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>Bloggs, Fred</t>
+  </si>
+  <si>
+    <t>Jones, Susan</t>
+  </si>
+  <si>
+    <t>Vivaldi, Antonio</t>
+  </si>
+  <si>
+    <t>Jul-26, Emp No 114257, Bloggs, Fred, 0.25FTE, WFAU Science Archives</t>
+  </si>
+  <si>
+    <t>Original Transaction Reference</t>
+  </si>
+  <si>
+    <t>426_Payroll_170726_E114999_Subsistence_2026/07/01_2026/07/31</t>
+  </si>
+  <si>
+    <t>426_Payroll_170726_E114666_Subsistence_2026/07/01_2026/07/31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +291,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -296,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -346,11 +367,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF777777"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF777777"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF777777"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF777777"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -403,6 +439,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1047,7 +1092,7 @@
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="7.1640625" customWidth="1"/>
-    <col min="11" max="11" width="5.5" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" customWidth="1"/>
     <col min="13" max="13" width="6.6640625" customWidth="1"/>
     <col min="14" max="14" width="12.1640625" style="15" customWidth="1"/>
@@ -1055,11 +1100,12 @@
     <col min="17" max="17" width="9.83203125" customWidth="1"/>
     <col min="18" max="18" width="9.1640625" customWidth="1"/>
     <col min="19" max="19" width="6.1640625" customWidth="1"/>
-    <col min="20" max="20" width="11.5" customWidth="1"/>
-    <col min="21" max="21" width="64" customWidth="1"/>
+    <col min="20" max="20" width="27.1640625" customWidth="1"/>
+    <col min="21" max="21" width="31" customWidth="1"/>
+    <col min="22" max="22" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1080,8 +1126,9 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" ht="19" x14ac:dyDescent="0.2">
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>15</v>
       </c>
@@ -1104,10 +1151,11 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>17</v>
@@ -1149,7 +1197,7 @@
         <v>29</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>30</v>
@@ -1164,10 +1212,13 @@
         <v>33</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -1194,7 +1245,9 @@
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
       <c r="N4" s="14" t="s">
@@ -1213,11 +1266,12 @@
         <v>0</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T4" s="6"/>
+      <c r="U4" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
@@ -1244,7 +1298,9 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
       <c r="N5" s="16" t="s">
@@ -1263,11 +1319,12 @@
         <v>0</v>
       </c>
       <c r="S5" s="6"/>
-      <c r="T5" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T5" s="6"/>
+      <c r="U5" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>14</v>
       </c>
@@ -1294,7 +1351,9 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="K6" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L6" s="6"/>
       <c r="M6" s="5"/>
       <c r="N6" s="16" t="s">
@@ -1313,11 +1372,12 @@
         <v>0</v>
       </c>
       <c r="S6" s="6"/>
-      <c r="T6" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T6" s="6"/>
+      <c r="U6" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -1344,7 +1404,9 @@
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L7" s="6"/>
       <c r="M7" s="5"/>
       <c r="N7" s="16" t="s">
@@ -1363,11 +1425,12 @@
         <v>0</v>
       </c>
       <c r="S7" s="6"/>
-      <c r="T7" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T7" s="6"/>
+      <c r="U7" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1394,7 +1457,9 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="5"/>
       <c r="N8" s="16" t="s">
@@ -1413,11 +1478,12 @@
         <v>0</v>
       </c>
       <c r="S8" s="6"/>
-      <c r="T8" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T8" s="6"/>
+      <c r="U8" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
@@ -1444,7 +1510,9 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="19" t="s">
+        <v>64</v>
+      </c>
       <c r="L9" s="6"/>
       <c r="M9" s="5"/>
       <c r="N9" s="16" t="s">
@@ -1461,11 +1529,12 @@
         <v>0</v>
       </c>
       <c r="S9" s="6"/>
-      <c r="T9" s="5" t="s">
+      <c r="T9" s="6"/>
+      <c r="U9" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
@@ -1476,7 +1545,7 @@
         <v>34</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>41</v>
@@ -1496,7 +1565,7 @@
       <c r="L10" s="6"/>
       <c r="M10" s="5"/>
       <c r="N10" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O10" s="7">
         <v>600</v>
@@ -1511,9 +1580,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6"/>
-      <c r="T10" s="11"/>
-    </row>
-    <row r="11" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T10" s="6"/>
+      <c r="U10" s="11"/>
+    </row>
+    <row r="11" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1544,7 +1614,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="5"/>
       <c r="N11" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O11" s="7">
         <v>500</v>
@@ -1559,9 +1629,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6"/>
-      <c r="T11" s="11"/>
-    </row>
-    <row r="12" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T11" s="6"/>
+      <c r="U11" s="11"/>
+    </row>
+    <row r="12" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>56</v>
       </c>
@@ -1588,11 +1659,13 @@
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="19" t="s">
+        <v>65</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="5"/>
       <c r="N12" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O12" s="7">
         <v>3300</v>
@@ -1607,11 +1680,12 @@
         <v>0</v>
       </c>
       <c r="S12" s="6"/>
-      <c r="T12" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T12" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="U12" s="11"/>
+    </row>
+    <row r="13" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>56</v>
       </c>
@@ -1638,7 +1712,9 @@
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="K13" s="20" t="s">
+        <v>64</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="5"/>
       <c r="N13" s="16" t="s">
@@ -1657,11 +1733,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="6"/>
-      <c r="T13" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T13" s="6"/>
+      <c r="U13" s="11"/>
+    </row>
+    <row r="14" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -1688,11 +1763,13 @@
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="20" t="s">
+        <v>64</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="5"/>
       <c r="N14" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O14" s="7">
         <v>3000</v>
@@ -1707,11 +1784,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="6"/>
-      <c r="T14" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T14" s="6"/>
+      <c r="U14" s="11"/>
+    </row>
+    <row r="15" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
@@ -1722,7 +1798,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>41</v>
@@ -1738,11 +1814,13 @@
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="20" t="s">
+        <v>64</v>
+      </c>
       <c r="L15" s="6"/>
       <c r="M15" s="5"/>
       <c r="N15" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O15" s="7">
         <v>2000</v>
@@ -1757,11 +1835,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="6"/>
-      <c r="T15" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T15" s="6"/>
+      <c r="U15" s="11"/>
+    </row>
+    <row r="16" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>56</v>
       </c>
@@ -1788,7 +1865,9 @@
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="L16" s="6"/>
       <c r="M16" s="5"/>
       <c r="N16" s="16" t="s">
@@ -1807,11 +1886,12 @@
         <v>0</v>
       </c>
       <c r="S16" s="6"/>
-      <c r="T16" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" s="11"/>
+    </row>
+    <row r="17" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>56</v>
       </c>
@@ -1838,7 +1918,9 @@
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="K17" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="L17" s="6"/>
       <c r="M17" s="5"/>
       <c r="N17" s="16" t="s">
@@ -1857,11 +1939,12 @@
         <v>0</v>
       </c>
       <c r="S17" s="6"/>
-      <c r="T17" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T17" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="U17" s="11"/>
+    </row>
+    <row r="18" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>56</v>
       </c>
@@ -1888,7 +1971,9 @@
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="5"/>
       <c r="N18" s="16" t="s">
@@ -1907,11 +1992,12 @@
         <v>0</v>
       </c>
       <c r="S18" s="6"/>
-      <c r="T18" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="64" x14ac:dyDescent="0.2">
+      <c r="T18" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="U18" s="11"/>
+    </row>
+    <row r="19" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>56</v>
       </c>
@@ -1938,7 +2024,9 @@
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="19" t="s">
+        <v>66</v>
+      </c>
       <c r="L19" s="6"/>
       <c r="M19" s="5"/>
       <c r="N19" s="16" t="s">
@@ -1957,9 +2045,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="6"/>
-      <c r="T19" s="11" t="s">
-        <v>64</v>
-      </c>
+      <c r="T19" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="U19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3776B028-3EBA-F449-A8A7-092790244520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738B8A76-9508-BA49-8AA3-60E4A2821C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="600" windowWidth="33460" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="2380" windowWidth="29720" windowHeight="15980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Commitments" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$V$19</definedName>
     <definedName name="page\x2dtotal">Commitments!$A$17</definedName>
     <definedName name="page\x2dtotal\x2dmaster0">Commitments!$A$17</definedName>
   </definedNames>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="72">
   <si>
     <t>PROJECT SUMMARY</t>
   </si>
@@ -246,6 +247,9 @@
   </si>
   <si>
     <t>426_Payroll_170726_E114666_Subsistence_2026/07/01_2026/07/31</t>
+  </si>
+  <si>
+    <t>Expenditure Item Date</t>
   </si>
 </sst>
 </file>
@@ -386,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -434,12 +438,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -447,6 +445,25 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -799,12 +816,12 @@
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:21" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1047,27 +1064,27 @@
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1080,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1095,17 +1112,18 @@
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" customWidth="1"/>
     <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" style="15" customWidth="1"/>
-    <col min="15" max="16" width="9.1640625" customWidth="1"/>
-    <col min="17" max="17" width="9.83203125" customWidth="1"/>
-    <col min="18" max="18" width="9.1640625" customWidth="1"/>
-    <col min="19" max="19" width="6.1640625" customWidth="1"/>
-    <col min="20" max="20" width="27.1640625" customWidth="1"/>
-    <col min="21" max="21" width="31" customWidth="1"/>
-    <col min="22" max="22" width="64" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="25" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" style="15" customWidth="1"/>
+    <col min="16" max="17" width="9.1640625" customWidth="1"/>
+    <col min="18" max="18" width="9.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" customWidth="1"/>
+    <col min="20" max="20" width="6.1640625" customWidth="1"/>
+    <col min="21" max="21" width="27.1640625" customWidth="1"/>
+    <col min="22" max="22" width="31" customWidth="1"/>
+    <col min="23" max="23" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1119,22 +1137,23 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="1"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="12"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-    </row>
-    <row r="2" spans="1:21" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" ht="19" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1144,16 +1163,17 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="1"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="12"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
-    </row>
-    <row r="3" spans="1:21" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>61</v>
       </c>
@@ -1193,32 +1213,35 @@
       <c r="M3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>14</v>
       </c>
@@ -1245,33 +1268,36 @@
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="26">
+        <v>44832</v>
+      </c>
+      <c r="O4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="7">
+      <c r="P4" s="7">
         <v>5208</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
       <c r="R4" s="7">
         <v>0</v>
       </c>
-      <c r="S4" s="6"/>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
       <c r="T4" s="6"/>
-      <c r="U4" s="11" t="s">
+      <c r="U4" s="6"/>
+      <c r="V4" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
@@ -1298,33 +1324,36 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="26">
+        <v>44893</v>
+      </c>
+      <c r="O5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="7">
+      <c r="P5" s="7">
         <v>5208</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
       <c r="R5" s="7">
         <v>0</v>
       </c>
-      <c r="S5" s="6"/>
+      <c r="S5" s="7">
+        <v>0</v>
+      </c>
       <c r="T5" s="6"/>
-      <c r="U5" s="11" t="s">
+      <c r="U5" s="6"/>
+      <c r="V5" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>14</v>
       </c>
@@ -1351,33 +1380,36 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="26">
+        <v>44893</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="7">
+      <c r="P6" s="7">
         <v>5208</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
       <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
       <c r="T6" s="6"/>
-      <c r="U6" s="11" t="s">
+      <c r="U6" s="6"/>
+      <c r="V6" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -1404,33 +1436,36 @@
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="26">
+        <v>44954</v>
+      </c>
+      <c r="O7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O7" s="7">
+      <c r="P7" s="7">
         <v>5208</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="Q7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
       <c r="R7" s="7">
         <v>0</v>
       </c>
-      <c r="S7" s="6"/>
+      <c r="S7" s="7">
+        <v>0</v>
+      </c>
       <c r="T7" s="6"/>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="6"/>
+      <c r="V7" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1457,33 +1492,36 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O8" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="7">
+      <c r="P8" s="7">
         <v>5208</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
       <c r="R8" s="7">
         <v>0</v>
       </c>
-      <c r="S8" s="6"/>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
       <c r="T8" s="6"/>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="6"/>
+      <c r="V8" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
@@ -1510,31 +1548,34 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="17" t="s">
         <v>64</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O9" s="7">
+      <c r="P9" s="7">
         <v>500</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="Q9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
       <c r="T9" s="6"/>
-      <c r="U9" s="5" t="s">
+      <c r="U9" s="6"/>
+      <c r="V9" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
@@ -1564,26 +1605,29 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="26">
+        <v>45013</v>
+      </c>
+      <c r="O10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="O10" s="7">
+      <c r="P10" s="7">
         <v>600</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
       <c r="R10" s="7">
         <v>0</v>
       </c>
-      <c r="S10" s="6"/>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="11"/>
-    </row>
-    <row r="11" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="U10" s="6"/>
+      <c r="V10" s="11"/>
+    </row>
+    <row r="11" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -1613,26 +1657,29 @@
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="5"/>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="26">
+        <v>45013</v>
+      </c>
+      <c r="O11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="O11" s="7">
+      <c r="P11" s="7">
         <v>500</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="Q11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
       <c r="R11" s="7">
         <v>0</v>
       </c>
-      <c r="S11" s="6"/>
+      <c r="S11" s="7">
+        <v>0</v>
+      </c>
       <c r="T11" s="6"/>
-      <c r="U11" s="11"/>
-    </row>
-    <row r="12" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="U11" s="6"/>
+      <c r="V11" s="11"/>
+    </row>
+    <row r="12" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>56</v>
       </c>
@@ -1659,33 +1706,36 @@
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="17" t="s">
         <v>65</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="7">
+      <c r="P12" s="7">
         <v>3300</v>
       </c>
-      <c r="P12" s="5" t="s">
+      <c r="Q12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
       <c r="R12" s="7">
         <v>0</v>
       </c>
-      <c r="S12" s="6"/>
-      <c r="T12" s="21" t="s">
+      <c r="S12" s="7">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6"/>
+      <c r="U12" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="U12" s="11"/>
-    </row>
-    <row r="13" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="V12" s="11"/>
+    </row>
+    <row r="13" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>56</v>
       </c>
@@ -1712,31 +1762,34 @@
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="18" t="s">
         <v>64</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="26">
+        <v>44954</v>
+      </c>
+      <c r="O13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O13" s="7">
+      <c r="P13" s="7">
         <v>3300</v>
       </c>
-      <c r="P13" s="5" t="s">
+      <c r="Q13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
       <c r="R13" s="7">
         <v>0</v>
       </c>
-      <c r="S13" s="6"/>
+      <c r="S13" s="7">
+        <v>0</v>
+      </c>
       <c r="T13" s="6"/>
-      <c r="U13" s="11"/>
-    </row>
-    <row r="14" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="U13" s="6"/>
+      <c r="V13" s="11"/>
+    </row>
+    <row r="14" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -1763,31 +1816,34 @@
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="18" t="s">
         <v>64</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="16" t="s">
+      <c r="N14" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O14" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="O14" s="7">
+      <c r="P14" s="7">
         <v>3000</v>
       </c>
-      <c r="P14" s="5" t="s">
+      <c r="Q14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
       <c r="R14" s="7">
         <v>0</v>
       </c>
-      <c r="S14" s="6"/>
+      <c r="S14" s="7">
+        <v>0</v>
+      </c>
       <c r="T14" s="6"/>
-      <c r="U14" s="11"/>
-    </row>
-    <row r="15" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="U14" s="6"/>
+      <c r="V14" s="11"/>
+    </row>
+    <row r="15" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
@@ -1814,31 +1870,34 @@
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="18" t="s">
         <v>64</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="16" t="s">
+      <c r="N15" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="7">
+      <c r="P15" s="7">
         <v>2000</v>
       </c>
-      <c r="P15" s="5" t="s">
+      <c r="Q15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
       <c r="R15" s="7">
         <v>0</v>
       </c>
-      <c r="S15" s="6"/>
+      <c r="S15" s="7">
+        <v>0</v>
+      </c>
       <c r="T15" s="6"/>
-      <c r="U15" s="11"/>
-    </row>
-    <row r="16" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="U15" s="6"/>
+      <c r="V15" s="11"/>
+    </row>
+    <row r="16" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>56</v>
       </c>
@@ -1865,33 +1924,36 @@
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="17" t="s">
         <v>66</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="16" t="s">
+      <c r="N16" s="26">
+        <v>44832</v>
+      </c>
+      <c r="O16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O16" s="7">
+      <c r="P16" s="7">
         <v>6000</v>
       </c>
-      <c r="P16" s="5" t="s">
+      <c r="Q16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
       <c r="R16" s="7">
         <v>0</v>
       </c>
-      <c r="S16" s="6"/>
-      <c r="T16" s="21" t="s">
+      <c r="S16" s="7">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="U16" s="11"/>
-    </row>
-    <row r="17" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="V16" s="11"/>
+    </row>
+    <row r="17" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>56</v>
       </c>
@@ -1918,33 +1980,36 @@
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="19" t="s">
+      <c r="K17" s="17" t="s">
         <v>66</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="16" t="s">
+      <c r="N17" s="26">
+        <v>44832</v>
+      </c>
+      <c r="O17" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="O17" s="7">
+      <c r="P17" s="7">
         <v>6000</v>
       </c>
-      <c r="P17" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
       <c r="R17" s="7">
         <v>0</v>
       </c>
-      <c r="S17" s="6"/>
-      <c r="T17" s="21" t="s">
+      <c r="S17" s="7">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6"/>
+      <c r="U17" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="U17" s="11"/>
-    </row>
-    <row r="18" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="V17" s="11"/>
+    </row>
+    <row r="18" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>56</v>
       </c>
@@ -1971,33 +2036,36 @@
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="17" t="s">
         <v>66</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="16" t="s">
+      <c r="N18" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O18" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="O18" s="7">
+      <c r="P18" s="7">
         <v>6000</v>
       </c>
-      <c r="P18" s="5" t="s">
+      <c r="Q18" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
       <c r="R18" s="7">
         <v>0</v>
       </c>
-      <c r="S18" s="6"/>
-      <c r="T18" s="21" t="s">
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6"/>
+      <c r="U18" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="U18" s="11"/>
-    </row>
-    <row r="19" spans="1:21" ht="64" x14ac:dyDescent="0.2">
+      <c r="V18" s="11"/>
+    </row>
+    <row r="19" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>56</v>
       </c>
@@ -2024,31 +2092,34 @@
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="17" t="s">
         <v>66</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="16" t="s">
+      <c r="N19" s="26">
+        <v>44770</v>
+      </c>
+      <c r="O19" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O19" s="7">
+      <c r="P19" s="7">
         <v>6000</v>
       </c>
-      <c r="P19" s="5" t="s">
+      <c r="Q19" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
       <c r="R19" s="7">
         <v>0</v>
       </c>
-      <c r="S19" s="6"/>
-      <c r="T19" s="21" t="s">
+      <c r="S19" s="7">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6"/>
+      <c r="U19" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2106,12 +2177,12 @@
       <c r="T1" s="8"/>
     </row>
     <row r="2" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -2460,50 +2531,50 @@
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738B8A76-9508-BA49-8AA3-60E4A2821C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2CF5CE-31C2-DE40-A759-5C99AE9557FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="2380" windowWidth="29720" windowHeight="15980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3640" yWindow="1280" windowWidth="32060" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Commitments" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$H$19</definedName>
     <definedName name="page\x2dtotal">Commitments!$A$17</definedName>
     <definedName name="page\x2dtotal\x2dmaster0">Commitments!$A$17</definedName>
   </definedNames>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
   <si>
     <t>PROJECT SUMMARY</t>
   </si>
@@ -90,30 +90,12 @@
     <t>Organization</t>
   </si>
   <si>
-    <t>Task Number</t>
-  </si>
-  <si>
     <t>Expenditure Category</t>
   </si>
   <si>
     <t>Expenditure Type</t>
   </si>
   <si>
-    <t>Transaction Type</t>
-  </si>
-  <si>
-    <t>Transaction Number</t>
-  </si>
-  <si>
-    <t>Document Entry</t>
-  </si>
-  <si>
-    <t>Supplier Name</t>
-  </si>
-  <si>
-    <t>Invoice Number</t>
-  </si>
-  <si>
     <t>Originator</t>
   </si>
   <si>
@@ -126,30 +108,9 @@
     <t>Accounting Period</t>
   </si>
   <si>
-    <t>Project Currency</t>
-  </si>
-  <si>
-    <t>Project Currency Amount</t>
-  </si>
-  <si>
-    <t>Paid Amount</t>
-  </si>
-  <si>
-    <t>Paid Date</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Oct-22</t>
   </si>
   <si>
-    <t>GBP</t>
-  </si>
-  <si>
-    <t>University of Edinburgh</t>
-  </si>
-  <si>
     <t>Dec-22</t>
   </si>
   <si>
@@ -157,21 +118,6 @@
   </si>
   <si>
     <t>Research Assistant</t>
-  </si>
-  <si>
-    <t>Research Assistant-Payroll Allowances</t>
-  </si>
-  <si>
-    <t>Miscellaneous Expenditure</t>
-  </si>
-  <si>
-    <t>3881284</t>
-  </si>
-  <si>
-    <t>Miscellaneous Expenditure Item</t>
-  </si>
-  <si>
-    <t>3837733</t>
   </si>
   <si>
     <t>6_2021_1811451_Ra4819 Indirect Costs</t>
@@ -256,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,12 +218,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -390,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -416,13 +356,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -435,16 +372,19 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -452,19 +392,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1097,1033 +1024,441 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" customWidth="1"/>
-    <col min="5" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="7.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="6.6640625" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="25" customWidth="1"/>
-    <col min="15" max="15" width="12.1640625" style="15" customWidth="1"/>
-    <col min="16" max="17" width="9.1640625" customWidth="1"/>
-    <col min="18" max="18" width="9.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" customWidth="1"/>
-    <col min="20" max="20" width="6.1640625" customWidth="1"/>
-    <col min="21" max="21" width="27.1640625" customWidth="1"/>
-    <col min="22" max="22" width="31" customWidth="1"/>
-    <col min="23" max="23" width="64" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="7" max="7" width="27.1640625" customWidth="1"/>
+    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="9" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22" ht="19" x14ac:dyDescent="0.2">
+      <c r="D1" s="1"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-    </row>
-    <row r="3" spans="1:22" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="19">
+        <v>44832</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="F4" s="7">
+        <v>5208</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19">
+        <v>44893</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="7">
+        <v>5208</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="19">
+        <v>44893</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="F6" s="7">
+        <v>5208</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="19">
+        <v>44954</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5208</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7">
+        <v>5208</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="C9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="7">
+        <v>500</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="19">
+        <v>45013</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="7">
+        <v>600</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="19">
+        <v>45013</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="7">
+        <v>500</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="O3" s="13" t="s">
+      <c r="C12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="7">
+        <v>3300</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="19">
+        <v>44954</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="7">
+        <v>3300</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="7">
+        <v>3000</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="19">
+        <v>44832</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="7">
+        <v>6000</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="19">
+        <v>44832</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="26">
-        <v>44832</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="7">
-        <v>5208</v>
-      </c>
-      <c r="Q4" s="5" t="s">
+      <c r="F17" s="7">
+        <v>6000</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="7">
+        <v>6000</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="19">
+        <v>44770</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="7">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="26">
-        <v>44893</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="7">
-        <v>5208</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7">
-        <v>0</v>
-      </c>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="26">
-        <v>44893</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="7">
-        <v>5208</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
-      </c>
-      <c r="S6" s="7">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="26">
-        <v>44954</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" s="7">
-        <v>5208</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
-      </c>
-      <c r="S7" s="7">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" s="7">
-        <v>5208</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="7">
-        <v>0</v>
-      </c>
-      <c r="S8" s="7">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O9" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" s="7">
-        <v>500</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="26">
-        <v>45013</v>
-      </c>
-      <c r="O10" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="P10" s="7">
-        <v>600</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
-      </c>
-      <c r="S10" s="7">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="11"/>
-    </row>
-    <row r="11" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="26">
-        <v>45013</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="P11" s="7">
-        <v>500</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
-      </c>
-      <c r="S11" s="7">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="11"/>
-    </row>
-    <row r="12" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="P12" s="7">
-        <v>3300</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0</v>
-      </c>
-      <c r="S12" s="7">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="V12" s="11"/>
-    </row>
-    <row r="13" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="26">
-        <v>44954</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="P13" s="7">
-        <v>3300</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R13" s="7">
-        <v>0</v>
-      </c>
-      <c r="S13" s="7">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="11"/>
-    </row>
-    <row r="14" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O14" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="P14" s="7">
-        <v>3000</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
-      </c>
-      <c r="S14" s="7">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="11"/>
-    </row>
-    <row r="15" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" s="7">
-        <v>2000</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R15" s="7">
-        <v>0</v>
-      </c>
-      <c r="S15" s="7">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="11"/>
-    </row>
-    <row r="16" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="26">
-        <v>44832</v>
-      </c>
-      <c r="O16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="P16" s="7">
+      <c r="F19" s="7">
         <v>6000</v>
       </c>
-      <c r="Q16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R16" s="7">
-        <v>0</v>
-      </c>
-      <c r="S16" s="7">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6"/>
-      <c r="U16" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="V16" s="11"/>
-    </row>
-    <row r="17" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="26">
-        <v>44832</v>
-      </c>
-      <c r="O17" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="P17" s="7">
-        <v>6000</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R17" s="7">
-        <v>0</v>
-      </c>
-      <c r="S17" s="7">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6"/>
-      <c r="U17" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="V17" s="11"/>
-    </row>
-    <row r="18" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O18" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="7">
-        <v>6000</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R18" s="7">
-        <v>0</v>
-      </c>
-      <c r="S18" s="7">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6"/>
-      <c r="U18" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="V18" s="11"/>
-    </row>
-    <row r="19" spans="1:22" ht="64" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="26">
-        <v>44770</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="P19" s="7">
-        <v>6000</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
-      </c>
-      <c r="S19" s="7">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6"/>
-      <c r="U19" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="V19" s="11"/>
+      <c r="G19" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2178,7 +1513,7 @@
     </row>
     <row r="2" spans="1:20" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2223,38 +1558,38 @@
       <c r="T3" s="1"/>
     </row>
     <row r="4" spans="1:20" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="1"/>

--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2CF5CE-31C2-DE40-A759-5C99AE9557FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A369D0-AB48-E441-965B-70B4DD98F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="1280" windowWidth="32060" windowHeight="15300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6440" yWindow="1320" windowWidth="23500" windowHeight="19300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Commitments" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$I$40</definedName>
     <definedName name="page\x2dtotal">Commitments!$A$17</definedName>
     <definedName name="page\x2dtotal\x2dmaster0">Commitments!$A$17</definedName>
   </definedNames>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="64">
   <si>
     <t>PROJECT SUMMARY</t>
   </si>
@@ -147,18 +147,12 @@
     <t>Jan-23</t>
   </si>
   <si>
-    <t>Feb-23</t>
-  </si>
-  <si>
     <t>11111995_11111999</t>
   </si>
   <si>
     <t>Consumables - Telephone and Communication</t>
   </si>
   <si>
-    <t>Apr-23</t>
-  </si>
-  <si>
     <t>Sep-22</t>
   </si>
   <si>
@@ -196,13 +190,49 @@
   </si>
   <si>
     <t>Expenditure Item Date</t>
+  </si>
+  <si>
+    <t>426_Payroll_170726_E114666-2_Universities Superannuation Scheme Employer Contributions_2026/07/01_2026/07/31</t>
+  </si>
+  <si>
+    <t>Mozart, Amadeus</t>
+  </si>
+  <si>
+    <t>Bach, Johan</t>
+  </si>
+  <si>
+    <t>ToyGaia</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Venice</t>
+  </si>
+  <si>
+    <t>Mar-22</t>
+  </si>
+  <si>
+    <t>Apr-22</t>
+  </si>
+  <si>
+    <t>May-22</t>
+  </si>
+  <si>
+    <t>Jun-22</t>
+  </si>
+  <si>
+    <t>Jul-22</t>
+  </si>
+  <si>
+    <t>Feb-22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,13 +272,28 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +303,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD6EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.24994659260841701"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -330,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -368,9 +425,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -381,11 +435,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -743,12 +851,12 @@
       <c r="T1" s="1"/>
     </row>
     <row r="2" spans="1:21" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -991,27 +1099,27 @@
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1024,441 +1132,1011 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="13" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" customWidth="1"/>
-    <col min="7" max="7" width="27.1640625" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="9" width="64" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="43.83203125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="1"/>
       <c r="E1" s="11"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" ht="19" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="1"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="1"/>
       <c r="E2" s="11"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="19">
-        <v>44832</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="7">
-        <v>5208</v>
-      </c>
-      <c r="G4" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="22">
+        <v>44801</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="H4" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="19">
-        <v>44893</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7">
-        <v>5208</v>
-      </c>
-      <c r="G5" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="22">
+        <v>44832</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="H5" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="19">
-        <v>44893</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="7">
-        <v>5208</v>
-      </c>
-      <c r="G6" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="22">
+        <v>44862</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="23">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="H6" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="19">
-        <v>44954</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5208</v>
-      </c>
-      <c r="G7" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="22">
+        <v>44862</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="23">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>44</v>
+      </c>
       <c r="H7" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="7">
-        <v>5208</v>
-      </c>
-      <c r="G8" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="22">
+        <v>44893</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="H8" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="7">
-        <v>500</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="22">
+        <v>44923</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="22">
+        <v>44954</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="29"/>
+    </row>
+    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="22">
+        <v>44648</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="22">
+        <v>44679</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="22">
+        <v>44709</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="22">
+        <v>44740</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="22">
+        <v>44770</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="22">
+        <v>44801</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="29"/>
+    </row>
+    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="22">
+        <v>44801</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="22">
+        <v>44862</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="22">
+        <v>44893</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="1:9" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="36"/>
+    </row>
+    <row r="23" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="22">
+        <v>44648</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="22">
+        <v>44679</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="22">
+        <v>44709</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="22">
+        <v>44740</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="22">
+        <v>44770</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="22">
+        <v>44801</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="23">
+        <v>1500</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="22">
+        <v>44832</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="19">
-        <v>45013</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="7">
-        <v>600</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="19">
-        <v>45013</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="7">
-        <v>500</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="7">
-        <v>3300</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="F29" s="23">
+        <v>3000</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="10"/>
+      <c r="I29" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="22">
+        <v>44862</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="23">
+        <v>3000</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="22">
+        <v>44893</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="23">
+        <v>3000</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="22">
+        <v>44923</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="23">
+        <v>3000</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="22">
+        <v>44954</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="23">
+        <v>3000</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="29"/>
+    </row>
+    <row r="35" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="22">
+        <v>44589</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G35" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="19">
-        <v>44954</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="7">
-        <v>3300</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="H35" s="10"/>
+      <c r="I35" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="22">
+        <v>44620</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G36" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="7">
-        <v>3000</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="H36" s="10"/>
+      <c r="I36" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A37" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="22">
+        <v>44648</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="23">
+        <v>5000</v>
+      </c>
+      <c r="G37" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="7">
-        <v>2000</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="19">
-        <v>44832</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="H37" s="10"/>
+      <c r="I37" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="22">
+        <v>44679</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="23">
         <v>6000</v>
       </c>
-      <c r="G16" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="19">
-        <v>44832</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="G38" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="22">
+        <v>44709</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="23">
         <v>6000</v>
       </c>
-      <c r="G17" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="G39" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="10"/>
+      <c r="I39" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="22">
+        <v>44740</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="23">
         <v>6000</v>
       </c>
-      <c r="G18" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="19">
-        <v>44770</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="7">
-        <v>6000</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="10"/>
+      <c r="G40" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="10"/>
+      <c r="I40" s="20" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1512,12 +2190,12 @@
       <c r="T1" s="8"/>
     </row>
     <row r="2" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1866,50 +2544,50 @@
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/toydata/transactions.xlsx
+++ b/toydata/transactions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A369D0-AB48-E441-965B-70B4DD98F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6440" yWindow="1320" windowWidth="23500" windowHeight="19300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="600" windowWidth="23500" windowHeight="19300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Summary" sheetId="1" r:id="rId1"/>
